--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260703.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260703.xlsx
@@ -755,17 +755,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>51,465</t>
+          <t>213,019,080</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -777,17 +777,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>213,019,080</t>
+          <t>51,465</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
